--- a/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2012/PENNSYLVANIA_2012.xlsx
+++ b/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2012/PENNSYLVANIA_2012.xlsx
@@ -1669,7 +1669,7 @@
         <v>40</v>
       </c>
       <c r="D73">
-        <v>0.009803921568627</v>
+        <v>0.009803921568627002</v>
       </c>
     </row>
     <row r="74">
@@ -1687,7 +1687,7 @@
         <v>40</v>
       </c>
       <c r="D74">
-        <v>0.009803921568627</v>
+        <v>0.009803921568627002</v>
       </c>
     </row>
     <row r="75">
@@ -2004,7 +2004,7 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Allende</t>
+          <t>San Miguel De Allende</t>
         </is>
       </c>
       <c r="C92">
@@ -8780,7 +8780,7 @@
       </c>
       <c r="B469" t="inlineStr">
         <is>
-          <t>San Juan Mixtepec - Distr. 08 -</t>
+          <t>San Juan Mixtepec -Dto. 08 -</t>
         </is>
       </c>
       <c r="C469">
@@ -14198,7 +14198,7 @@
       </c>
       <c r="B770" t="inlineStr">
         <is>
-          <t>Tuxpam</t>
+          <t>Tuxpan</t>
         </is>
       </c>
       <c r="C770">
